--- a/Assets/Resources/117.72.179.129/《别墅七日》文案/对话表格.xlsx
+++ b/Assets/Resources/117.72.179.129/《别墅七日》文案/对话表格.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hz_zy\Desktop\117.72.179.129\《别墅七日》文案\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2AE6E7-9015-4B94-A88D-E298141BB250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD11FFC-D3CE-4DAB-A51D-F17C9FAD5319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -92,10 +95,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>玩家</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>dialogue</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -180,11 +179,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1&lt;好。&gt;=1008&lt;br&gt;2&lt;还是算了吧。&gt;=1019</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1&lt;询问洛夫莱斯家族的历史。&gt;=1011&lt;br&gt;2&lt;询问教授口中的雕塑。&gt;=1014&lt;br&gt;3&lt;询问奇怪的藏品。&gt;=1015&lt;br&gt;4&lt;没什么想问的了。&gt;=1017</t>
+    <t>null</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1&lt;好。&gt;=1001&lt;br&gt;2&lt;还是算了吧。&gt;=1012</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1&lt;询问洛夫莱斯家族的历史。&gt;=1004&lt;br&gt;2&lt;询问教授口中的雕塑。&gt;=1007&lt;br&gt;3&lt;询问奇怪的藏品。&gt;=1008&lt;br&gt;4&lt;没什么想问的了。&gt;=1010</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -614,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
@@ -645,7 +652,7 @@
     </row>
     <row r="2" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -657,15 +664,15 @@
         <v>8</v>
       </c>
       <c r="E2" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
@@ -677,15 +684,15 @@
         <v>9</v>
       </c>
       <c r="E3" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
@@ -697,15 +704,15 @@
         <v>10</v>
       </c>
       <c r="E4" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
@@ -717,18 +724,18 @@
         <v>11</v>
       </c>
       <c r="E5" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -737,475 +744,594 @@
         <v>12</v>
       </c>
       <c r="E6" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1009</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1010</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>1010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1012</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1013</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1010</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1010</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1016</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1010</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>1017</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1018</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>1018</v>
-      </c>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>1019</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1020</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1021</v>
-      </c>
-      <c r="F21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>1021</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1010</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1023</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>1023</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1024</v>
-      </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>1024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1025</v>
-      </c>
-      <c r="F25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>1025</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1026</v>
-      </c>
-      <c r="F26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>1026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>1027</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="2">
-        <v>1028</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>1028</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="5"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB51CFF-C086-4570-A13E-96E28642286E}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1005</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1006</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1003</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1009</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1003</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1013</v>
+      </c>
+      <c r="F14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1014</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1003</v>
+      </c>
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F813CD1-8251-414A-ADBB-481B5791A79E}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="37.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1004</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9038C27E-209D-4135-BDBC-4BE166F7FF7C}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>